--- a/data/b2_candoi/B2 Candói 02-2026.xlsx
+++ b/data/b2_candoi/B2 Candói 02-2026.xlsx
@@ -4420,43 +4420,43 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>459.27</v>
+        <v>466.84</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Reparo elétrico</t>
+          <t>Salários do mês anterior</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>1834.5</v>
+        <v>57162.61</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46058</v>
+        <v>46060</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Salários do mês anterior</t>
+          <t>Reparo elétrico</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>58432.18</v>
+        <v>2119.51</v>
       </c>
     </row>
     <row r="5">
@@ -4465,52 +4465,52 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Tarifas bancárias</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>3748.49</v>
+        <v>900.12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46063</v>
+        <v>46061</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Sistemas e contabilidade</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Sistema de automação e contabilidade</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>3200</v>
+        <v>3954.27</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="n">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Sistemas e contabilidade</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Seguro do posto</t>
+          <t>Sistema de automação e contabilidade</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>1633.37</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="8">
@@ -4528,25 +4528,25 @@
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>959.11</v>
+        <v>856.03</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Energia elétrica</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Troca de filtros das bombas</t>
+          <t>Conta de energia</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>1711.3</v>
+        <v>9420.450000000001</v>
       </c>
     </row>
     <row r="10">
@@ -4555,16 +4555,16 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Energia elétrica</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Conta de energia</t>
+          <t>Placas, redes sociais e brindes</t>
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>8422.15</v>
+        <v>1076.99</v>
       </c>
     </row>
     <row r="11">
@@ -4573,34 +4573,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Placas, redes sociais e brindes</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>824.38</v>
+        <v>3930.45</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46068</v>
+        <v>46071</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Seguro do posto</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>3778.65</v>
+        <v>958.01</v>
       </c>
     </row>
     <row r="13">
@@ -4618,61 +4618,61 @@
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>20316.08</v>
+        <v>20254.86</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46073</v>
+        <v>46075</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Material de limpeza e escritório</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>1171.81</v>
+        <v>4014.53</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Coleta de resíduos (óleo e borra)</t>
+          <t>Limpeza da caixa separadora</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>1271.39</v>
+        <v>2318.25</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46075</v>
+        <v>46078</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Fretes</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Frete das entregas de combustível</t>
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>3983.71</v>
+        <v>8140</v>
       </c>
     </row>
     <row r="17">
@@ -4681,16 +4681,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fretes</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Frete das entregas de combustível</t>
+          <t>Coleta de resíduos (óleo e borra)</t>
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>8140</v>
+        <v>598.5599999999999</v>
       </c>
     </row>
     <row r="18">
@@ -4708,7 +4708,7 @@
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>3453.22</v>
+        <v>3550.32</v>
       </c>
     </row>
   </sheetData>
